--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -1729,40 +1729,120 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al-Shabab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Al-Ahli</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -1845,22 +1845,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -1903,22 +1903,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M26" t="n">
+        <v>14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>15</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -1961,22 +1961,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M27" t="n">
+        <v>16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>13</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2019,22 +2019,62 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Al-Ahli</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M28" t="n">
+        <v>12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2077,22 +2077,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2135,22 +2135,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Al Okhdood</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M30" t="n">
+        <v>14</v>
+      </c>
+      <c r="N30" t="n">
+        <v>14</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2193,22 +2193,62 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2251,22 +2251,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M32" t="n">
+        <v>15</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2309,22 +2309,62 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M33" t="n">
+        <v>15</v>
+      </c>
+      <c r="N33" t="n">
+        <v>16</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2367,22 +2367,62 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Al Fayha</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M34" t="n">
+        <v>14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>

--- a/new-stats/damac-fc.xlsx
+++ b/new-stats/damac-fc.xlsx
@@ -2425,22 +2425,62 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Al-Nassr</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Damac</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
